--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2021_T1_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2021_T1_0.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="50">
   <si>
     <t/>
   </si>
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>76</t>
+    <t>70</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,109 +57,112 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
+    <t>0.129</t>
+  </si>
+  <si>
+    <t>(0.040)</t>
+  </si>
+  <si>
+    <t>0.600</t>
+  </si>
+  <si>
+    <t>(0.059)</t>
+  </si>
+  <si>
+    <t>0.300</t>
+  </si>
+  <si>
+    <t>(0.055)</t>
+  </si>
+  <si>
+    <t>0.257</t>
+  </si>
+  <si>
+    <t>(0.095)</t>
+  </si>
+  <si>
+    <t>1.557</t>
+  </si>
+  <si>
+    <t>(0.233)</t>
+  </si>
+  <si>
+    <t>0.486</t>
+  </si>
+  <si>
+    <t>(0.111)</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (2) </t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0.150</t>
+  </si>
+  <si>
+    <t>(0.057)</t>
+  </si>
+  <si>
+    <t>0.850</t>
+  </si>
+  <si>
+    <t>0.675</t>
+  </si>
+  <si>
+    <t>(0.075)</t>
+  </si>
+  <si>
+    <t>0.375</t>
+  </si>
+  <si>
+    <t>(0.231)</t>
+  </si>
+  <si>
+    <t>4.050</t>
+  </si>
+  <si>
+    <t>(0.580)</t>
+  </si>
+  <si>
+    <t>1.650</t>
+  </si>
+  <si>
+    <t>(0.315)</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>(2)-(1)</t>
+  </si>
+  <si>
+    <t>Pairwise t-test</t>
+  </si>
+  <si>
+    <t>Mean difference</t>
+  </si>
+  <si>
+    <t>0.021</t>
+  </si>
+  <si>
+    <t>0.250***</t>
+  </si>
+  <si>
+    <t>0.375***</t>
+  </si>
+  <si>
     <t>0.118</t>
   </si>
   <si>
-    <t>(0.037)</t>
-  </si>
-  <si>
-    <t>0.553</t>
-  </si>
-  <si>
-    <t>(0.057)</t>
-  </si>
-  <si>
-    <t>0.276</t>
-  </si>
-  <si>
-    <t>(0.052)</t>
-  </si>
-  <si>
-    <t>0.237</t>
-  </si>
-  <si>
-    <t>(0.088)</t>
-  </si>
-  <si>
-    <t>1.434</t>
-  </si>
-  <si>
-    <t>(0.220)</t>
-  </si>
-  <si>
-    <t>0.447</t>
-  </si>
-  <si>
-    <t>(0.103)</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (2) </t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0.150</t>
-  </si>
-  <si>
-    <t>0.850</t>
-  </si>
-  <si>
-    <t>0.675</t>
-  </si>
-  <si>
-    <t>(0.075)</t>
-  </si>
-  <si>
-    <t>0.375</t>
-  </si>
-  <si>
-    <t>(0.231)</t>
-  </si>
-  <si>
-    <t>4.050</t>
-  </si>
-  <si>
-    <t>(0.580)</t>
-  </si>
-  <si>
-    <t>1.650</t>
-  </si>
-  <si>
-    <t>(0.315)</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>(2)-(1)</t>
-  </si>
-  <si>
-    <t>Pairwise t-test</t>
-  </si>
-  <si>
-    <t>Mean difference</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>0.297***</t>
-  </si>
-  <si>
-    <t>0.399***</t>
-  </si>
-  <si>
-    <t>0.138</t>
-  </si>
-  <si>
-    <t>2.616***</t>
-  </si>
-  <si>
-    <t>1.203***</t>
+    <t>2.493***</t>
+  </si>
+  <si>
+    <t>1.164***</t>
   </si>
 </sst>
 </file>
@@ -226,7 +229,7 @@
         <v>0</v>
       </c>
       <c r="G1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2">
@@ -249,7 +252,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -272,7 +275,7 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -292,10 +295,10 @@
         <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
@@ -312,7 +315,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
         <v>0</v>
@@ -335,13 +338,13 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -358,7 +361,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
         <v>0</v>
@@ -381,13 +384,13 @@
         <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -404,7 +407,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
         <v>0</v>
@@ -427,13 +430,13 @@
         <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -450,7 +453,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
         <v>0</v>
@@ -473,13 +476,13 @@
         <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -496,7 +499,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
         <v>0</v>
@@ -519,13 +522,13 @@
         <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -542,7 +545,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F15" t="s">
         <v>0</v>
